--- a/output/pdf_financials_xlsx/FMM.xlsx
+++ b/output/pdf_financials_xlsx/FMM.xlsx
@@ -5875,7 +5875,7 @@
         <v>-0.028432</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.114017</v>
       </c>
       <c r="F91" s="3" t="n">
         <v>0</v>
@@ -5927,52 +5927,52 @@
         <v>4.771539</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>5.494227</v>
+        <v>5.236339</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>6.099307</v>
+        <v>5.806693</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.852723</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.052425</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.068158</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.068158</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>6.068158</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>6.068158</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.068158</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.068158</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.068158</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.068158</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>6.068158</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.068158</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.068158</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>6.068158</v>
       </c>
     </row>
     <row r="93">
@@ -6315,7 +6315,7 @@
         <v>-0.934765</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>2.70315</v>
+        <v>-2.70315</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-0.313907</v>
@@ -9480,7 +9480,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -9969,7 +9973,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10252,7 +10260,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -10852,7 +10864,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -12141,7 +12157,11 @@
           <t>Share-based payments reserve (note 7(d))</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -12933,7 +12953,11 @@
           <t>Share-based payments reserve (note 8(d))</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -13717,7 +13741,11 @@
           <t>Share-based payments reserve (note 8(d))</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -15418,7 +15446,11 @@
           <t>Share-based payments reserve (note 8(d))</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -16784,7 +16816,11 @@
           <t>Investments revaluation reserve (note 4)</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -17788,7 +17824,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -25339,7 +25379,7 @@
         <v>-0.934765</v>
       </c>
       <c r="K170" s="5" t="n">
-        <v>2.70315</v>
+        <v>-2.70315</v>
       </c>
       <c r="L170" s="5" t="n">
         <v>-0.313907</v>

--- a/output/pdf_financials_xlsx/FMM.xlsx
+++ b/output/pdf_financials_xlsx/FMM.xlsx
@@ -1029,25 +1029,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.045473</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.007289</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.012872</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.009127</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004697</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00033</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000191</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000488</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -1975,25 +1975,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.935056</v>
+        <v>-2.980529</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.470438</v>
+        <v>-6.477727</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-8.29482</v>
+        <v>-8.307691999999999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.205485</v>
+        <v>-1.214612</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.488739</v>
+        <v>-2.493436</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.934765</v>
+        <v>-0.935095</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.70315</v>
+        <v>2.702959</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.313907</v>
@@ -2020,7 +2020,7 @@
         <v>-0.477043</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.449138</v>
+        <v>-0.449626</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>-0.472636</v>
@@ -2091,25 +2091,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.935056</v>
+        <v>-2.980529</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.470438</v>
+        <v>-6.477727</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-8.29482</v>
+        <v>-8.307691999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.205485</v>
+        <v>-1.214612</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.488739</v>
+        <v>-2.493436</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.934765</v>
+        <v>-0.935095</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.70315</v>
+        <v>2.702959</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.313907</v>
@@ -2136,7 +2136,7 @@
         <v>-0.476449</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.448663</v>
+        <v>-0.449151</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-0.472256</v>
@@ -2419,34 +2419,34 @@
         <v>0.01779</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.084399</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.006582</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.007419</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.05378</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.004883</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.898604</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.18602</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.021963</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.002282</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.005803</v>
       </c>
     </row>
     <row r="35">
@@ -2535,34 +2535,34 @@
         <v>0.05529</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.00495</v>
+        <v>0.089349</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.006582</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.007419</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.05378</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.004883</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.898604</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.18602</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.021963</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.002282</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.005803</v>
       </c>
     </row>
     <row r="37">
@@ -3231,34 +3231,34 @@
         <v>0.01361</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.084399</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.006582</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.007419</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.23578</v>
+        <v>0.182</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.186883</v>
+        <v>0.182</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.110064</v>
+        <v>0.21146</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.189052</v>
+        <v>0.003032</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.021963</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.002282</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.005803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -37813,7 +37813,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -38658,7 +38658,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -39721,7 +39721,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -51639,7 +51639,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -56942,7 +56942,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -60833,7 +60833,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E528" s="5" t="n">

--- a/output/pdf_financials_xlsx/FMM.xlsx
+++ b/output/pdf_financials_xlsx/FMM.xlsx
@@ -7060,7 +7060,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.022427</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -32492,7 +32492,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -33696,7 +33700,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FMM.xlsx
+++ b/output/pdf_financials_xlsx/FMM.xlsx
@@ -745,19 +745,19 @@
         <v>0.363431</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.328143</v>
+        <v>0.343143</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.863059</v>
+        <v>0.8991170000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.563057</v>
+        <v>0.599121</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.071688</v>
+        <v>0.108476</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.018913</v>
+        <v>0.026212</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>0</v>
@@ -6959,7 +6959,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>-0.000319</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -7225,13 +7225,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.128529</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.426028</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.225992</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -7240,16 +7240,16 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.029492</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.04008</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.013251</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -26495,7 +26495,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -26790,7 +26794,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -31494,7 +31502,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -31898,7 +31910,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E237" s="5" t="n">
         <v>7.17415</v>
       </c>
@@ -34708,7 +34724,11 @@
           <t>Proceeds from disposal of marketable securities</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E265" s="5" t="n">
         <v>0.128529</v>
       </c>
@@ -45909,7 +45929,11 @@
           <t>Directors fees (note 10)</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -45941,7 +45965,7 @@
         </is>
       </c>
       <c r="K378" s="5" t="n">
-        <v>-0.007299</v>
+        <v>0.007299</v>
       </c>
       <c r="L378" t="inlineStr">
         <is>
@@ -50459,7 +50483,11 @@
           <t>Directors fees (note 10(a))</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -50489,7 +50517,7 @@
         <v>0.036788</v>
       </c>
       <c r="K424" s="5" t="n">
-        <v>-0.007299</v>
+        <v>0.007299</v>
       </c>
       <c r="L424" t="inlineStr">
         <is>
@@ -53350,7 +53378,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -59249,7 +59281,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E512" t="inlineStr">
         <is>
           <t>-</t>
